--- a/public/data/kiadas.xlsx
+++ b/public/data/kiadas.xlsx
@@ -128,12 +128,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -326,248 +330,294 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="22.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="28.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="22.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="28.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>44.78</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>24.04</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>48.21</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>25.41</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>10.14</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
         <v>2019</v>
       </c>
-      <c r="B2" s="1" t="n">
-        <v>68</v>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="D2" s="1" t="n">
+      <c r="B4" s="2" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="G2" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="H2" s="1" t="n">
+      <c r="E4" s="2" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="H4" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
         <v>2020</v>
       </c>
-      <c r="B3" s="1" t="n">
-        <v>64</v>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="H3" s="1" t="n">
+      <c r="B5" s="2" t="n">
+        <v>64.32</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>31.13</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="H5" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
         <v>2021</v>
       </c>
-      <c r="B4" s="1" t="n">
-        <v>84</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="H4" s="1" t="n">
+      <c r="B6" s="2" t="n">
+        <v>84.31</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="H6" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="B5" s="1" t="n">
-        <v>85</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H5" s="1" t="n">
+      <c r="B7" s="2" t="n">
+        <v>85.52</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>27.96</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>24.28</v>
+      </c>
+      <c r="H7" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="B6" s="1" t="n">
-        <v>113</v>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>49</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="H6" s="1" t="n">
+      <c r="B8" s="2" t="n">
+        <v>113.46</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>25.68</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>49.06</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>32.78</v>
+      </c>
+      <c r="H8" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="B7" s="1" t="n">
-        <v>83</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="H7" s="1" t="n">
+      <c r="B9" s="2" t="n">
+        <v>83.13</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>27.07</v>
+      </c>
+      <c r="H9" s="2" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="B8" s="1" t="n">
-        <v>97</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="H8" s="1" t="n">
+      <c r="B10" s="2" t="n">
+        <v>97.25</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>33.92</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>33.59</v>
+      </c>
+      <c r="H10" s="2" t="n">
         <v>7000</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
         <v>2026</v>
       </c>
-      <c r="B9" s="1" t="n">
-        <v>101</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="H9" s="1" t="n">
+      <c r="B11" s="2" t="n">
+        <v>101.29</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>27.37</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>37.55</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="H11" s="2" t="n">
         <v>7000</v>
       </c>
     </row>

--- a/public/data/kiadas.xlsx
+++ b/public/data/kiadas.xlsx
@@ -372,22 +372,25 @@
         <v>2017</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>44.78</v>
+        <v>44780</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>9.57</v>
+        <v>9570</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>1.7</v>
+        <v>1700</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>24.04</v>
+        <v>24040</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>1.74</v>
+        <v>1740</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>7.73</v>
+        <v>7730</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -395,22 +398,25 @@
         <v>2018</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>48.21</v>
+        <v>48210</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>9.9</v>
+        <v>9900</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>1.87</v>
+        <v>1870</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>25.41</v>
+        <v>25410</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>0.89</v>
+        <v>892</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>10.14</v>
+        <v>10140</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -418,22 +424,22 @@
         <v>2019</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>68.3</v>
+        <v>68300</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>11.82</v>
+        <v>11820</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2</v>
+        <v>2000</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>39.16</v>
+        <v>39160</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2.85</v>
+        <v>2850</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>12.47</v>
+        <v>12470</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>0</v>
@@ -444,22 +450,22 @@
         <v>2020</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>64.32</v>
+        <v>64320</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>16.07</v>
+        <v>16070</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2.45</v>
+        <v>2450</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>31.13</v>
+        <v>31130</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2.4</v>
+        <v>2400</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>12.27</v>
+        <v>12270</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>0</v>
@@ -470,22 +476,22 @@
         <v>2021</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>84.31</v>
+        <v>84310</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>16.68</v>
+        <v>16680</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2.57</v>
+        <v>2570</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>49.8</v>
+        <v>49800</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2.07</v>
+        <v>2070</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>13.19</v>
+        <v>13190</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>0</v>
@@ -496,22 +502,22 @@
         <v>2022</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>85.52</v>
+        <v>85520</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>26.46</v>
+        <v>26460</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>3.5</v>
+        <v>3500</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>27.96</v>
+        <v>27960</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>3.37</v>
+        <v>3370</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>24.28</v>
+        <v>24280</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>0</v>
@@ -522,22 +528,22 @@
         <v>2023</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>113.46</v>
+        <v>113460</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>25.68</v>
+        <v>25680</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>3.34</v>
+        <v>3340</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>49.06</v>
+        <v>49060</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2.6</v>
+        <v>2600</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>32.78</v>
+        <v>32780</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>0</v>
@@ -548,22 +554,22 @@
         <v>2024</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>83.13</v>
+        <v>83130</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>18.96</v>
+        <v>18960</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2.58</v>
+        <v>2580</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>31.74</v>
+        <v>31740</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>2.78</v>
+        <v>2780</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>27.07</v>
+        <v>27070</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>0</v>
@@ -574,22 +580,22 @@
         <v>2025</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>97.25</v>
+        <v>97250</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>25.15</v>
+        <v>25120</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>3.24</v>
+        <v>3240</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>33.92</v>
+        <v>33920</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1.35</v>
+        <v>1350</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>33.59</v>
+        <v>33590</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>7000</v>
@@ -600,22 +606,22 @@
         <v>2026</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>101.29</v>
+        <v>101290</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>27.37</v>
+        <v>27370</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>3.62</v>
+        <v>3620</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>37.55</v>
+        <v>37550</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1.5</v>
+        <v>1500</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>31.25</v>
+        <v>31250</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>7000</v>

--- a/public/data/kiadas.xlsx
+++ b/public/data/kiadas.xlsx
@@ -372,22 +372,22 @@
         <v>2017</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>44780</v>
+        <v>44780000</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>9570</v>
+        <v>9570000</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>1700</v>
+        <v>1700000</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>24040</v>
+        <v>24040000</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>1740</v>
+        <v>1740000</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>7730</v>
+        <v>7730000</v>
       </c>
       <c r="H2" s="1" t="n">
         <v>0</v>
@@ -398,22 +398,22 @@
         <v>2018</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>48210</v>
+        <v>48210000</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>9900</v>
+        <v>9900000</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>1870</v>
+        <v>1870000</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>25410</v>
+        <v>25410000</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>892</v>
+        <v>892000</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>10140</v>
+        <v>10140000</v>
       </c>
       <c r="H3" s="1" t="n">
         <v>0</v>
@@ -424,22 +424,22 @@
         <v>2019</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>68300</v>
+        <v>68300000</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>11820</v>
+        <v>11820000</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>2000</v>
+        <v>2000000</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>39160</v>
+        <v>39160000</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2850</v>
+        <v>2850000</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>12470</v>
+        <v>12470000</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>0</v>
@@ -450,22 +450,22 @@
         <v>2020</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>64320</v>
+        <v>64320000</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>16070</v>
+        <v>16070000</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2450</v>
+        <v>2450000</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>31130</v>
+        <v>31130000</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2400</v>
+        <v>2400000</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>12270</v>
+        <v>12270000</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>0</v>
@@ -476,22 +476,22 @@
         <v>2021</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>84310</v>
+        <v>84310000</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>16680</v>
+        <v>16680000</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2570</v>
+        <v>2570000</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>49800</v>
+        <v>49800000</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2070</v>
+        <v>2070000</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>13190</v>
+        <v>13190000</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>0</v>
@@ -502,22 +502,22 @@
         <v>2022</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>85520</v>
+        <v>85520000</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>26460</v>
+        <v>26460000</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>3500</v>
+        <v>3500000</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>27960</v>
+        <v>27960000</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>3370</v>
+        <v>3370000</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>24280</v>
+        <v>24280000</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>0</v>
@@ -528,22 +528,22 @@
         <v>2023</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>113460</v>
+        <v>113460000</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>25680</v>
+        <v>25680000</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>3340</v>
+        <v>3340000</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>49060</v>
+        <v>49060000</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2600</v>
+        <v>2600000</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>32780</v>
+        <v>32780000</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>0</v>
@@ -554,22 +554,22 @@
         <v>2024</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>83130</v>
+        <v>83130000</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>18960</v>
+        <v>18960000</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2580</v>
+        <v>2580000</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>31740</v>
+        <v>31740000</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>2780</v>
+        <v>2780000</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>27070</v>
+        <v>27070000</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>0</v>
@@ -580,22 +580,22 @@
         <v>2025</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>97250</v>
+        <v>97250000</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>25120</v>
+        <v>25120000</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>3240</v>
+        <v>3240000</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>33920</v>
+        <v>33920000</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1350</v>
+        <v>1350000</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>33590</v>
+        <v>33590000</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>7000</v>
@@ -606,22 +606,22 @@
         <v>2026</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>101290</v>
+        <v>101290000</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>27370</v>
+        <v>27370000</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>3620</v>
+        <v>3620000</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>37550</v>
+        <v>37550000</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1500</v>
+        <v>1500000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>31250</v>
+        <v>31250000</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>7000</v>

--- a/public/data/kiadas.xlsx
+++ b/public/data/kiadas.xlsx
@@ -598,7 +598,7 @@
         <v>33590000</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>7000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -606,25 +606,25 @@
         <v>2026</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>101290000</v>
+        <v>101282932</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>27370000</v>
+        <v>27366246</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>3620000</v>
+        <v>3618703</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>37550000</v>
+        <v>27551668</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1500000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>31250000</v>
+        <v>21246315</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>7000</v>
+        <v>7000000</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/kiadas.xlsx
+++ b/public/data/kiadas.xlsx
@@ -580,22 +580,22 @@
         <v>2025</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>97250000</v>
+        <v>96924074</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>25120000</v>
+        <v>25152424</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>3240000</v>
+        <v>3235817</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>33920000</v>
+        <v>33602259</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1350000</v>
+        <v>1345000</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>33590000</v>
+        <v>33588574</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>7000000</v>
@@ -609,19 +609,21 @@
         <v>101282932</v>
       </c>
       <c r="C11" s="2" t="n">
+        <f aca="false">27366246</f>
         <v>27366246</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>3618703</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>27551668</v>
+        <v>37551668</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1500000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>21246315</v>
+        <f aca="false">31246315</f>
+        <v>31246315</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>7000000</v>

--- a/public/data/kiadas.xlsx
+++ b/public/data/kiadas.xlsx
@@ -583,7 +583,8 @@
         <v>96924074</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>25152424</v>
+        <f aca="false">25152424+25055449</f>
+        <v>50207873</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>3235817</v>
@@ -595,7 +596,8 @@
         <v>1345000</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>33588574</v>
+        <f aca="false">33588574-25055449</f>
+        <v>8533125</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>7000000</v>
@@ -609,8 +611,8 @@
         <v>101282932</v>
       </c>
       <c r="C11" s="2" t="n">
-        <f aca="false">27366246</f>
-        <v>27366246</v>
+        <f aca="false">27366246+22046315</f>
+        <v>49412561</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>3618703</v>
@@ -622,8 +624,8 @@
         <v>1500000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <f aca="false">31246315</f>
-        <v>31246315</v>
+        <f aca="false">31246315-22046315</f>
+        <v>9200000</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>7000000</v>

--- a/public/data/kiadas.xlsx
+++ b/public/data/kiadas.xlsx
@@ -502,22 +502,24 @@
         <v>2022</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>85520000</v>
+        <v>85519429</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>26460000</v>
+        <f aca="false">26463106+17938767</f>
+        <v>44401873</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>3500000</v>
+        <v>3446518</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>27960000</v>
+        <v>27963929</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>3370000</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>24280000</v>
+        <f aca="false">24275876-17938767</f>
+        <v>6337109</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>0</v>
@@ -528,22 +530,24 @@
         <v>2023</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>113460000</v>
+        <v>113460887</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>25680000</v>
+        <f aca="false">25684446+16458894</f>
+        <v>42143340</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>3340000</v>
+        <v>3335818</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>49060000</v>
+        <v>49057939</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>2600000</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>32780000</v>
+        <f aca="false">32782684-16458894</f>
+        <v>16323790</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>0</v>
@@ -554,22 +558,24 @@
         <v>2024</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>83130000</v>
+        <v>83125704</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>18960000</v>
+        <f aca="false">18958523+19347750</f>
+        <v>38306273</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2580000</v>
+        <v>2581900</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>31740000</v>
+        <v>31738767</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>2780000</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>27070000</v>
+        <f aca="false">27066514-19347750</f>
+        <v>7718764</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>0</v>

--- a/public/data/kiadas.xlsx
+++ b/public/data/kiadas.xlsx
@@ -505,14 +505,15 @@
         <v>85519429</v>
       </c>
       <c r="C7" s="2" t="n">
-        <f aca="false">26463106+17938767</f>
-        <v>44401873</v>
+        <f aca="false">26463106+17938767/2</f>
+        <v>35432489.5</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>3446518</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>27963929</v>
+        <f aca="false">27963929+17938767/2</f>
+        <v>36933312.5</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>3370000</v>
@@ -533,14 +534,15 @@
         <v>113460887</v>
       </c>
       <c r="C8" s="2" t="n">
-        <f aca="false">25684446+16458894</f>
-        <v>42143340</v>
+        <f aca="false">25684446+16458894/2</f>
+        <v>33913893</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>3335818</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>49057939</v>
+        <f aca="false">49057939+16458894/2</f>
+        <v>57287386</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>2600000</v>
@@ -561,14 +563,15 @@
         <v>83125704</v>
       </c>
       <c r="C9" s="2" t="n">
-        <f aca="false">18958523+19347750</f>
-        <v>38306273</v>
+        <f aca="false">18958523+19347750/2</f>
+        <v>28632398</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2581900</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>31738767</v>
+        <f aca="false">31738767+19347750/2</f>
+        <v>41412642</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>2780000</v>
@@ -589,14 +592,15 @@
         <v>96924074</v>
       </c>
       <c r="C10" s="2" t="n">
-        <f aca="false">25152424+25055449</f>
-        <v>50207873</v>
+        <f aca="false">25152424+25055449/2</f>
+        <v>37680148.5</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>3235817</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>33602259</v>
+        <f aca="false">33602259+25055449/2</f>
+        <v>46129983.5</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1345000</v>
@@ -617,14 +621,15 @@
         <v>101282932</v>
       </c>
       <c r="C11" s="2" t="n">
-        <f aca="false">27366246+22046315</f>
-        <v>49412561</v>
+        <f aca="false">27366246+22046315/2</f>
+        <v>38389403.5</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>3618703</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>37551668</v>
+        <f aca="false">37551668+22046315/2</f>
+        <v>48574825.5</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1500000</v>

--- a/public/data/kiadas.xlsx
+++ b/public/data/kiadas.xlsx
@@ -505,15 +505,14 @@
         <v>85519429</v>
       </c>
       <c r="C7" s="2" t="n">
-        <f aca="false">26463106+17938767/2</f>
-        <v>35432489.5</v>
+        <f aca="false">26463106+17938767</f>
+        <v>44401873</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>3446518</v>
       </c>
       <c r="E7" s="2" t="n">
-        <f aca="false">27963929+17938767/2</f>
-        <v>36933312.5</v>
+        <v>27963929</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>3370000</v>
@@ -534,15 +533,14 @@
         <v>113460887</v>
       </c>
       <c r="C8" s="2" t="n">
-        <f aca="false">25684446+16458894/2</f>
-        <v>33913893</v>
+        <f aca="false">25684446+16458894</f>
+        <v>42143340</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>3335818</v>
       </c>
       <c r="E8" s="2" t="n">
-        <f aca="false">49057939+16458894/2</f>
-        <v>57287386</v>
+        <v>49057939</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>2600000</v>
@@ -563,15 +561,14 @@
         <v>83125704</v>
       </c>
       <c r="C9" s="2" t="n">
-        <f aca="false">18958523+19347750/2</f>
-        <v>28632398</v>
+        <f aca="false">18958523+19347750</f>
+        <v>38306273</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2581900</v>
       </c>
       <c r="E9" s="2" t="n">
-        <f aca="false">31738767+19347750/2</f>
-        <v>41412642</v>
+        <v>31738767</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>2780000</v>
@@ -592,15 +589,14 @@
         <v>96924074</v>
       </c>
       <c r="C10" s="2" t="n">
-        <f aca="false">25152424+25055449/2</f>
-        <v>37680148.5</v>
+        <f aca="false">25152424+25055449</f>
+        <v>50207873</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>3235817</v>
       </c>
       <c r="E10" s="2" t="n">
-        <f aca="false">33602259+25055449/2</f>
-        <v>46129983.5</v>
+        <v>33602259</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1345000</v>
@@ -621,15 +617,14 @@
         <v>101282932</v>
       </c>
       <c r="C11" s="2" t="n">
-        <f aca="false">27366246+22046315/2</f>
-        <v>38389403.5</v>
+        <f aca="false">27366246+22046315</f>
+        <v>49412561</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>3618703</v>
       </c>
       <c r="E11" s="2" t="n">
-        <f aca="false">37551668+22046315/2</f>
-        <v>48574825.5</v>
+        <v>37551668</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1500000</v>

--- a/public/data/kiadas.xlsx
+++ b/public/data/kiadas.xlsx
@@ -372,22 +372,24 @@
         <v>2017</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>44780000</v>
+        <v>44744281</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>9570000</v>
+        <f aca="false">9574941+6565680</f>
+        <v>16140621</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>1700000</v>
+        <v>1697031</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>24040000</v>
+        <v>24035629</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>1740000</v>
+        <v>1739540</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>7730000</v>
+        <f aca="false">7697140-6565680</f>
+        <v>1131460</v>
       </c>
       <c r="H2" s="1" t="n">
         <v>0</v>
@@ -398,22 +400,24 @@
         <v>2018</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>48210000</v>
+        <v>48251151</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>9900000</v>
+        <f aca="false">9900246+7535589</f>
+        <v>17435835</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>1870000</v>
+        <v>1874560</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>25410000</v>
+        <v>25405711</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>892000</v>
+        <v>892195</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>10140000</v>
+        <f aca="false">10178439-7535589</f>
+        <v>2642850</v>
       </c>
       <c r="H3" s="1" t="n">
         <v>0</v>
@@ -424,22 +428,24 @@
         <v>2019</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>68300000</v>
+        <v>68306604</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>11820000</v>
+        <f aca="false">11824225+10201654</f>
+        <v>22025879</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2000000</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>39160000</v>
+        <v>39157218</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2850000</v>
+        <v>2851680</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>12470000</v>
+        <f aca="false">12473481-10201654</f>
+        <v>2271827</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>0</v>
@@ -450,22 +456,24 @@
         <v>2020</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>64320000</v>
+        <v>64319304</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>16070000</v>
+        <f aca="false">16071088+7341488</f>
+        <v>23412576</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2450000</v>
+        <v>2451333</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>31130000</v>
+        <v>31132255</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2400000</v>
+        <v>2395000</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>12270000</v>
+        <f aca="false">12269628-7341488</f>
+        <v>4928140</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>0</v>
@@ -476,22 +484,24 @@
         <v>2021</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>84310000</v>
+        <v>84311139</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>16680000</v>
+        <f aca="false">16681801+10463924</f>
+        <v>27145725</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2570000</v>
+        <v>2568798</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>49800000</v>
+        <v>49801716</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2070000</v>
+        <v>2065000</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>13190000</v>
+        <f aca="false">13193824-10463924</f>
+        <v>2729900</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>0</v>

--- a/public/data/kiadas.xlsx
+++ b/public/data/kiadas.xlsx
@@ -20,30 +20,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t xml:space="preserve">Év</t>
   </si>
   <si>
-    <t xml:space="preserve">Összes kiadás (eFt)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Személyi jellegű (eFt)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Munkaadói járulék (eFt)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dologi kiadás (eFt)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pénzbeni juttatás (eFt)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Egyéb kiadás (eFt)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Szolidaritási hozzájárulás (eFt)</t>
+    <t xml:space="preserve">Összes kiadás (Ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Személyi jellegű (Ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Munkaadói járulék (Ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dologi kiadás (Ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pénzbeni juttatás (Ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egyéb kiadás (Ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Szolidaritási hozzájárulás (Ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Közös Önkormányzati Hivatal (Ft)</t>
   </si>
 </sst>
 </file>
@@ -330,7 +333,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.83"/>
@@ -339,6 +342,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="28.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="28.65"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -366,6 +370,9 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="0" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
@@ -375,8 +382,8 @@
         <v>44744281</v>
       </c>
       <c r="C2" s="1" t="n">
-        <f aca="false">9574941+6565680</f>
-        <v>16140621</v>
+        <f aca="false">9574941</f>
+        <v>9574941</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>1697031</v>
@@ -388,11 +395,14 @@
         <v>1739540</v>
       </c>
       <c r="G2" s="1" t="n">
-        <f aca="false">7697140-6565680</f>
-        <v>1131460</v>
+        <f aca="false">7697140</f>
+        <v>7697140</v>
       </c>
       <c r="H2" s="1" t="n">
         <v>0</v>
+      </c>
+      <c r="I2" s="1" t="n">
+        <v>5286396</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -403,8 +413,8 @@
         <v>48251151</v>
       </c>
       <c r="C3" s="1" t="n">
-        <f aca="false">9900246+7535589</f>
-        <v>17435835</v>
+        <f aca="false">9900246</f>
+        <v>9900246</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>1874560</v>
@@ -416,11 +426,15 @@
         <v>892195</v>
       </c>
       <c r="G3" s="1" t="n">
-        <f aca="false">10178439-7535589</f>
-        <v>2642850</v>
+        <f aca="false">10178439</f>
+        <v>10178439</v>
       </c>
       <c r="H3" s="1" t="n">
         <v>0</v>
+      </c>
+      <c r="I3" s="1" t="n">
+        <f aca="false">5296550+23317</f>
+        <v>5319867</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -431,8 +445,8 @@
         <v>68306604</v>
       </c>
       <c r="C4" s="2" t="n">
-        <f aca="false">11824225+10201654</f>
-        <v>22025879</v>
+        <f aca="false">11824225</f>
+        <v>11824225</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2000000</v>
@@ -444,11 +458,14 @@
         <v>2851680</v>
       </c>
       <c r="G4" s="2" t="n">
-        <f aca="false">12473481-10201654</f>
-        <v>2271827</v>
+        <f aca="false">12473481</f>
+        <v>12473481</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>6603459</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -459,8 +476,8 @@
         <v>64319304</v>
       </c>
       <c r="C5" s="2" t="n">
-        <f aca="false">16071088+7341488</f>
-        <v>23412576</v>
+        <f aca="false">16071088</f>
+        <v>16071088</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2451333</v>
@@ -472,11 +489,14 @@
         <v>2395000</v>
       </c>
       <c r="G5" s="2" t="n">
-        <f aca="false">12269628-7341488</f>
-        <v>4928140</v>
+        <f aca="false">12269628</f>
+        <v>12269628</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>6024579</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -487,8 +507,8 @@
         <v>84311139</v>
       </c>
       <c r="C6" s="2" t="n">
-        <f aca="false">16681801+10463924</f>
-        <v>27145725</v>
+        <f aca="false">16681801</f>
+        <v>16681801</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2568798</v>
@@ -500,11 +520,14 @@
         <v>2065000</v>
       </c>
       <c r="G6" s="2" t="n">
-        <f aca="false">13193824-10463924</f>
-        <v>2729900</v>
+        <f aca="false">13193824</f>
+        <v>13193824</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>8196731</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -515,8 +538,8 @@
         <v>85519429</v>
       </c>
       <c r="C7" s="2" t="n">
-        <f aca="false">26463106+17938767</f>
-        <v>44401873</v>
+        <f aca="false">26463106</f>
+        <v>26463106</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>3446518</v>
@@ -528,11 +551,14 @@
         <v>3370000</v>
       </c>
       <c r="G7" s="2" t="n">
-        <f aca="false">24275876-17938767</f>
-        <v>6337109</v>
+        <f aca="false">24275876</f>
+        <v>24275876</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>12263381</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -543,8 +569,8 @@
         <v>113460887</v>
       </c>
       <c r="C8" s="2" t="n">
-        <f aca="false">25684446+16458894</f>
-        <v>42143340</v>
+        <f aca="false">25684446</f>
+        <v>25684446</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>3335818</v>
@@ -556,11 +582,14 @@
         <v>2600000</v>
       </c>
       <c r="G8" s="2" t="n">
-        <f aca="false">32782684-16458894</f>
-        <v>16323790</v>
+        <f aca="false">32782684</f>
+        <v>32782684</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>15886054</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -571,8 +600,8 @@
         <v>83125704</v>
       </c>
       <c r="C9" s="2" t="n">
-        <f aca="false">18958523+19347750</f>
-        <v>38306273</v>
+        <f aca="false">18958523</f>
+        <v>18958523</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2581900</v>
@@ -584,11 +613,15 @@
         <v>2780000</v>
       </c>
       <c r="G9" s="2" t="n">
-        <f aca="false">27066514-19347750</f>
-        <v>7718764</v>
+        <f aca="false">27066514</f>
+        <v>27066514</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <f aca="false">17438500+4201205</f>
+        <v>21639705</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -599,8 +632,8 @@
         <v>96924074</v>
       </c>
       <c r="C10" s="2" t="n">
-        <f aca="false">25152424+25055449</f>
-        <v>50207873</v>
+        <f aca="false">25152424</f>
+        <v>25152424</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>3235817</v>
@@ -612,11 +645,14 @@
         <v>1345000</v>
       </c>
       <c r="G10" s="2" t="n">
-        <f aca="false">33588574-25055449</f>
-        <v>8533125</v>
+        <f aca="false">33588574</f>
+        <v>33588574</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>7000000</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -627,8 +663,8 @@
         <v>101282932</v>
       </c>
       <c r="C11" s="2" t="n">
-        <f aca="false">27366246+22046315</f>
-        <v>49412561</v>
+        <f aca="false">27366246</f>
+        <v>27366246</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>3618703</v>
@@ -640,11 +676,14 @@
         <v>1500000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <f aca="false">31246315-22046315</f>
-        <v>9200000</v>
+        <f aca="false">31246315</f>
+        <v>31246315</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>7000000</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/kiadas.xlsx
+++ b/public/data/kiadas.xlsx
@@ -589,7 +589,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>15886054</v>
+        <v>13800168</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -620,8 +620,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="1" t="n">
-        <f aca="false">17438500+4201205</f>
-        <v>21639705</v>
+        <v>15886054</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -652,7 +651,8 @@
         <v>7000000</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>0</v>
+        <f aca="false">17438500+4201205</f>
+        <v>21639705</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -683,7 +683,7 @@
         <v>7000000</v>
       </c>
       <c r="I11" s="1" t="n">
-        <v>0</v>
+        <v>16104364</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/kiadas.xlsx
+++ b/public/data/kiadas.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t xml:space="preserve">Év</t>
   </si>
@@ -47,6 +47,18 @@
   </si>
   <si>
     <t xml:space="preserve">Közös Önkormányzati Hivatal (Ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felhalmozási kiadások (Ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beruházások (Ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Felújítások (Ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egyéb felhalmozási (Ft)</t>
   </si>
 </sst>
 </file>
@@ -333,7 +345,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.83"/>
@@ -342,7 +354,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18.83"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="28.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="28.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="28.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="22.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="13.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="20.54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -370,8 +386,20 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -404,6 +432,19 @@
       <c r="I2" s="1" t="n">
         <v>5286396</v>
       </c>
+      <c r="J2" s="1" t="n">
+        <f aca="false">K2+L2+M2</f>
+        <v>11139415</v>
+      </c>
+      <c r="K2" s="1" t="n">
+        <v>4068489</v>
+      </c>
+      <c r="L2" s="1" t="n">
+        <v>3895587</v>
+      </c>
+      <c r="M2" s="1" t="n">
+        <v>3175339</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
@@ -436,6 +477,19 @@
         <f aca="false">5296550+23317</f>
         <v>5319867</v>
       </c>
+      <c r="J3" s="1" t="n">
+        <f aca="false">K3+L3+M3</f>
+        <v>17220361</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>11270897</v>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>5827939</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>121525</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
@@ -467,6 +521,19 @@
       <c r="I4" s="1" t="n">
         <v>6603459</v>
       </c>
+      <c r="J4" s="1" t="n">
+        <f aca="false">K4+L4+M4</f>
+        <v>29468426</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>8000137</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>19491028</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>1977261</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
@@ -498,6 +565,19 @@
       <c r="I5" s="1" t="n">
         <v>6024579</v>
       </c>
+      <c r="J5" s="1" t="n">
+        <f aca="false">K5+L5+M5</f>
+        <v>50690535</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>25642588</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>24948175</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>99772</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -529,6 +609,19 @@
       <c r="I6" s="1" t="n">
         <v>8196731</v>
       </c>
+      <c r="J6" s="1" t="n">
+        <f aca="false">K6+L6+M6</f>
+        <v>24654415</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>23876189</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>292223</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>486003</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
@@ -560,6 +653,19 @@
       <c r="I7" s="1" t="n">
         <v>12263381</v>
       </c>
+      <c r="J7" s="1" t="n">
+        <f aca="false">K7+L7+M7</f>
+        <v>27934766</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>25788303</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>1929869</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>216594</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
@@ -591,6 +697,19 @@
       <c r="I8" s="1" t="n">
         <v>13800168</v>
       </c>
+      <c r="J8" s="1" t="n">
+        <f aca="false">K8+L8+M8</f>
+        <v>39637850</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>36338404</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>3299446</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
@@ -622,6 +741,19 @@
       <c r="I9" s="1" t="n">
         <v>15886054</v>
       </c>
+      <c r="J9" s="1" t="n">
+        <f aca="false">K9+L9+M9</f>
+        <v>39699003</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>33699468</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>5999535</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
@@ -654,6 +786,19 @@
         <f aca="false">17438500+4201205</f>
         <v>21639705</v>
       </c>
+      <c r="J10" s="1" t="n">
+        <f aca="false">K10+L10+M10</f>
+        <v>31398177</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>29821785</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>1551392</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>25000</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
@@ -684,6 +829,10 @@
       </c>
       <c r="I11" s="1" t="n">
         <v>16104364</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <f aca="false">K11+L11+M11</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/kiadas.xlsx
+++ b/public/data/kiadas.xlsx
@@ -832,7 +832,16 @@
       </c>
       <c r="J11" s="1" t="n">
         <f aca="false">K11+L11+M11</f>
-        <v>0</v>
+        <v>234674873</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>138870841</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>95771889</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>32143</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/kiadas.xlsx
+++ b/public/data/kiadas.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t xml:space="preserve">Év</t>
   </si>
@@ -59,6 +59,18 @@
   </si>
   <si>
     <t xml:space="preserve">Egyéb felhalmozási (Ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dologi – közüzemi (Ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dologi – fenntartás (Ft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infláció (előző évi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infláció (kumulált 2013-tól)</t>
   </si>
 </sst>
 </file>
@@ -68,7 +80,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -92,6 +104,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
@@ -143,7 +162,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -153,6 +172,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -345,7 +368,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.83"/>
@@ -359,6 +382,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="13.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="20.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="19.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="22.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="16.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="23.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="1" width="10.49"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -401,6 +429,18 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
@@ -445,6 +485,19 @@
       <c r="M2" s="1" t="n">
         <v>3175339</v>
       </c>
+      <c r="N2" s="1" t="n">
+        <v>2083423</v>
+      </c>
+      <c r="O2" s="1" t="n">
+        <f aca="false">157812+2182846+482812+431375+106057+0+1736215+31942+435500+3331963+35000+2122340+0+0+0+765344</f>
+        <v>11819206</v>
+      </c>
+      <c r="P2" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q2" s="1" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
@@ -490,32 +543,45 @@
       <c r="M3" s="1" t="n">
         <v>121525</v>
       </c>
+      <c r="N3" s="1" t="n">
+        <v>2146354</v>
+      </c>
+      <c r="O3" s="1" t="n">
+        <f aca="false">147068+2244910+506608+331354+0+0+922208+7500+1367660+2423769+35000+1841782+0+0+467498</f>
+        <v>10295357</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>2019</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="3" t="n">
         <v>68306604</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="3" t="n">
         <f aca="false">11824225</f>
         <v>11824225</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="3" t="n">
         <v>2000000</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="3" t="n">
         <v>39157218</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="3" t="n">
         <v>2851680</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="3" t="n">
         <f aca="false">12473481</f>
         <v>12473481</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I4" s="1" t="n">
@@ -533,33 +599,46 @@
       </c>
       <c r="M4" s="1" t="n">
         <v>1977261</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>2317017</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <f aca="false">276839+3273940+301385+534802+290960+5042+2275466+113211+1532535+3515934+35000+2118271+76130+0+0+466119</f>
+        <v>14815634</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>5.37</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>2020</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="3" t="n">
         <v>64319304</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="3" t="n">
         <f aca="false">16071088</f>
         <v>16071088</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="3" t="n">
         <v>2451333</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="3" t="n">
         <v>31132255</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="3" t="n">
         <v>2395000</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="3" t="n">
         <f aca="false">12269628</f>
         <v>12269628</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="1" t="n">
@@ -577,33 +656,46 @@
       </c>
       <c r="M5" s="1" t="n">
         <v>99772</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>2562572</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <f aca="false">288097+3287254+50226+636083+436855+0+2946867+7990+2598678+5864401+0+0+3316594+12333+0+0+611495</f>
+        <v>20056873</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>8.95</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>2021</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="3" t="n">
         <v>84311139</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="3" t="n">
         <f aca="false">16681801</f>
         <v>16681801</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="3" t="n">
         <v>2568798</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="3" t="n">
         <v>49801716</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="3" t="n">
         <v>2065000</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="3" t="n">
         <f aca="false">13193824</f>
         <v>13193824</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="1" t="n">
@@ -621,33 +713,46 @@
       </c>
       <c r="M6" s="1" t="n">
         <v>486003</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>2761395</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <f aca="false">141147+2787894+0+395223+398330+2662109+0+2946277+8763961+4510+0+273193+1217+720460</f>
+        <v>19094321</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>12.55</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="3" t="n">
         <v>85519429</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="3" t="n">
         <f aca="false">26463106</f>
         <v>26463106</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="3" t="n">
         <v>3446518</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="3" t="n">
         <v>27963929</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="3" t="n">
         <v>3370000</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="3" t="n">
         <f aca="false">24275876</f>
         <v>24275876</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="1" t="n">
@@ -665,33 +770,46 @@
       </c>
       <c r="M7" s="1" t="n">
         <v>216594</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>4686024</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <f aca="false">293585+4229961+466364+365311+1600979+0+2893063+5967702+57467+0+3565455+729018</f>
+        <v>20168905</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>18.29</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="3" t="n">
         <v>113460887</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="3" t="n">
         <f aca="false">25684446</f>
         <v>25684446</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="3" t="n">
         <v>3335818</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="3" t="n">
         <v>49057939</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="3" t="n">
         <v>2600000</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="3" t="n">
         <f aca="false">32782684</f>
         <v>32782684</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="1" t="n">
@@ -709,33 +827,47 @@
       </c>
       <c r="M8" s="1" t="n">
         <v>3299446</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <f aca="false">6468216+770431+120339</f>
+        <v>7358986</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <f aca="false">125947+3272646+436954+429086+1629820+2598096+9894190+57719+4291406+976458</f>
+        <v>23712322</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>35.44</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="3" t="n">
         <v>83125704</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="3" t="n">
         <f aca="false">18958523</f>
         <v>18958523</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="3" t="n">
         <v>2581900</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="3" t="n">
         <v>31738767</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="3" t="n">
         <v>2780000</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="3" t="n">
         <f aca="false">27066514</f>
         <v>27066514</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="1" t="n">
@@ -753,33 +885,47 @@
       </c>
       <c r="M9" s="1" t="n">
         <v>5999535</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <f aca="false">3527309+1695044+314751</f>
+        <v>5537104</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <f aca="false">107838+3235865+116234+1468998+528000+440270++2232525+381899+2672256+6270847+176000+120000+0+793386+0+4007461+0+0+245598+885933</f>
+        <v>23683110</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>59.28</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>2025</v>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" s="3" t="n">
         <v>96924074</v>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="3" t="n">
         <f aca="false">25152424</f>
         <v>25152424</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="3" t="n">
         <v>3235817</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="3" t="n">
         <v>33602259</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="3" t="n">
         <v>1345000</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G10" s="3" t="n">
         <f aca="false">33588574</f>
         <v>33588574</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="3" t="n">
         <v>7000000</v>
       </c>
       <c r="I10" s="1" t="n">
@@ -798,33 +944,47 @@
       </c>
       <c r="M10" s="1" t="n">
         <v>25000</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <f aca="false">2854290+2336363+274173</f>
+        <v>5464826</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <f aca="false">211447+2839104+396549+376183+2434388+0+4420536+0+4200029+800000+817770+3911564+0+0+90928+769899</f>
+        <v>21268397</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>65.17</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>2026</v>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B11" s="3" t="n">
         <v>101282932</v>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="3" t="n">
         <f aca="false">27366246</f>
         <v>27366246</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="3" t="n">
         <v>3618703</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="3" t="n">
         <v>37551668</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="3" t="n">
         <v>1500000</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="G11" s="3" t="n">
         <f aca="false">31246315</f>
         <v>31246315</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="H11" s="3" t="n">
         <v>7000000</v>
       </c>
       <c r="I11" s="1" t="n">
@@ -842,6 +1002,20 @@
       </c>
       <c r="M11" s="1" t="n">
         <v>32143</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <f aca="false">3000000+2500000+500000</f>
+        <v>6000000</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <f aca="false">300000+3000000+500000+500000+3000000+0+5500000+0+5600000+1500000+400000+2000000+1938329+4500000+106299+129685+0+81000+265039+1200000</f>
+        <v>30520352</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>72.44</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/kiadas.xlsx
+++ b/public/data/kiadas.xlsx
@@ -906,17 +906,17 @@
         <v>2025</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>96924074</v>
+        <v>97241700</v>
       </c>
       <c r="C10" s="3" t="n">
-        <f aca="false">25152424</f>
-        <v>25152424</v>
+        <f aca="false">25152426</f>
+        <v>25152426</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>3235817</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>33602259</v>
+        <v>33919883</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>1345000</v>
@@ -934,10 +934,10 @@
       </c>
       <c r="J10" s="1" t="n">
         <f aca="false">K10+L10+M10</f>
-        <v>31398177</v>
+        <v>30477184</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>29821785</v>
+        <v>28900792</v>
       </c>
       <c r="L10" s="1" t="n">
         <v>1551392</v>
